--- a/output/reports/report.xlsx
+++ b/output/reports/report.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,10 +458,24 @@
         <v>88.98999786376953</v>
       </c>
       <c r="C2" t="n">
-        <v>61.63000106811523</v>
+        <v>51.61999893188477</v>
       </c>
       <c r="D2" t="n">
-        <v>14.38000011444092</v>
+        <v>15.47999954223633</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/report.xlsx
+++ b/output/reports/report.xlsx
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>88.98999786376953</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>51.61999893188477</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>15.47999954223633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -469,13 +469,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>31.18000030517578</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3.799999952316284</v>
       </c>
     </row>
   </sheetData>
